--- a/ValueSet-ng-hiv-partner-notification-plan-vs.xlsx
+++ b/ValueSet-ng-hiv-partner-notification-plan-vs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:22:49+01:00</t>
+    <t>2026-08-17T07:55:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ng-hiv-partner-notification-plan-vs.xlsx
+++ b/ValueSet-ng-hiv-partner-notification-plan-vs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T07:55:48+01:00</t>
+    <t>2026-08-17T13:27:53+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ng-hiv-partner-notification-plan-vs.xlsx
+++ b/ValueSet-ng-hiv-partner-notification-plan-vs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T13:27:53+01:00</t>
+    <t>2026-08-17T16:10:29+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
